--- a/inspection_forms/047_store_display_compliance_audit_form--inspection_forms.xlsx
+++ b/inspection_forms/047_store_display_compliance_audit_form--inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -912,12 +912,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -945,12 +945,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'overstocking'}</t>
+          <t>overstocking</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Overstocking'}</t>
+          <t>Overstocking</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'underselling'}</t>
+          <t>underselling</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Underselling'}</t>
+          <t>Underselling</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'shelf_placement_incorrect'}</t>
+          <t>shelf_placement_incorrect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Shelf placement incorrect'}</t>
+          <t>Shelf placement incorrect</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'merchandising_not_meeting_standards'}</t>
+          <t>merchandising_not_meeting_standards</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Merchandising not meeting standards'}</t>
+          <t>Merchandising not meeting standards</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'product_not_displayed_correctly'}</t>
+          <t>product_not_displayed_correctly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Product not displayed correctly'}</t>
+          <t>Product not displayed correctly</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'shelf_not_meeting_safety_and_security_standards'}</t>
+          <t>shelf_not_meeting_safety_and_security_standards</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Shelf not meeting safety and security standards'}</t>
+          <t>Shelf not meeting safety and security standards</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'product_placement_correct'}</t>
+          <t>product_placement_correct</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Product placement correct'}</t>
+          <t>Product placement correct</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'product_pricing_correct'}</t>
+          <t>product_pricing_correct</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Product pricing correct'}</t>
+          <t>Product pricing correct</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'shelf_facing_correct'}</t>
+          <t>shelf_facing_correct</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Shelf facing correct'}</t>
+          <t>Shelf facing correct</t>
         </is>
       </c>
     </row>
@@ -1132,29 +1132,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'category_correct'}</t>
+          <t>category_correct</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Category correct'}</t>
+          <t>Category correct</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>merchandising_standards_choices</t>
+          <t>product_availability_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'shelf_facing_correct'}</t>
+          <t>in_stock</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Shelf facing correct'}</t>
+          <t>In Stock</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'in_stock'}</t>
+          <t>low_stock</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'In Stock'}</t>
+          <t>Low Stock</t>
         </is>
       </c>
     </row>
@@ -1183,29 +1183,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'low_stock'}</t>
+          <t>out_of_stock</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Low Stock'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>product_availability_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>{'label':_'out_of_stock'}</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>{'label': 'Out of Stock'}</t>
+          <t>Out of Stock</t>
         </is>
       </c>
     </row>
